--- a/public/templates/inplace-bank-import-v1.xlsx
+++ b/public/templates/inplace-bank-import-v1.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Bank Transactions" sheetId="1" r:id="rId1"/>
+    <sheet name="הנחיות למילוי" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="42.83203125" customWidth="1"/>
@@ -431,9 +433,147 @@
         <v>reference</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="d">
+        <v>2026-01-15T02:00:00.000Z</v>
+      </c>
+      <c r="B3" t="str">
+        <v>שורת דוגמה — יש להחליף בנתוני התדפיס שלכם</v>
+      </c>
+      <c r="C3" t="str">
+        <v>debit</v>
+      </c>
+      <c r="D3">
+        <v>1250.5</v>
+      </c>
+      <c r="E3" t="str">
+        <v>REF-0001</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D12"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ייבוא תדפיס בנק — הנחיות למילוי</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>יש למלא את גיליון „Bank Transactions". אין לשנות בו את שתי השורות הראשונות.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שורה 3 בגיליון הנתונים היא שורת דוגמה. יש להחליף אותה בנתונים שלכם או למחוק אותה — קובץ שנשלח והדוגמה עדיין בתוכו נדחה.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עמודה בקובץ</v>
+      </c>
+      <c r="B5" t="str">
+        <v>מה למלא</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ערכים מותרים ופורמט</v>
+      </c>
+      <c r="D5" t="str">
+        <v>דוגמה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>transaction_date</v>
+      </c>
+      <c r="B6" t="str">
+        <v>תאריך התנועה</v>
+      </c>
+      <c r="C6" t="str">
+        <v>תא בפורמט תאריך — לא טקסט</v>
+      </c>
+      <c r="D6" t="str">
+        <v>15.01.2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>description</v>
+      </c>
+      <c r="B7" t="str">
+        <v>תיאור התנועה כפי שמופיע בתדפיס</v>
+      </c>
+      <c r="C7" t="str">
+        <v>טקסט חופשי, שדה חובה</v>
+      </c>
+      <c r="D7" t="str">
+        <v>שורת דוגמה — יש להחליף בנתוני התדפיס שלכם</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>direction</v>
+      </c>
+      <c r="B8" t="str">
+        <v>כיוון התנועה</v>
+      </c>
+      <c r="C8" t="str">
+        <v>debit לחיוב, credit לזיכוי — באנגלית ובאותיות קטנות</v>
+      </c>
+      <c r="D8" t="str">
+        <v>debit</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>amount</v>
+      </c>
+      <c r="B9" t="str">
+        <v>סכום התנועה</v>
+      </c>
+      <c r="C9" t="str">
+        <v>מספר חיובי, עד שתי ספרות אחרי הנקודה</v>
+      </c>
+      <c r="D9" t="str">
+        <v>1250.50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>reference</v>
+      </c>
+      <c r="B10" t="str">
+        <v>אסמכתה</v>
+      </c>
+      <c r="C10" t="str">
+        <v>טקסט, אפשר להשאיר ריק</v>
+      </c>
+      <c r="D10" t="str">
+        <v>REF-0001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אין עמודת מטבע: כל תדפיס נקלט כמטבע אחד, ILS. אין לערבב מטבעות בקובץ אחד.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D12"/>
   </ignoredErrors>
 </worksheet>
 </file>